--- a/Result/profitability/3308.xlsx
+++ b/Result/profitability/3308.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,16 +669,16 @@
         <v>0.08</v>
       </c>
       <c r="M2" t="n">
-        <v>0.19875</v>
+        <v>0.19375</v>
       </c>
       <c r="N2" t="n">
-        <v>12.99625</v>
+        <v>37.67</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.65</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2125</v>
+        <v>0.24125</v>
       </c>
       <c r="N3" t="n">
-        <v>30.945</v>
+        <v>43.9025</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.35</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3475</v>
+        <v>0.3375</v>
       </c>
       <c r="N4" t="n">
-        <v>37.64625</v>
+        <v>37.785</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.44</v>
       </c>
       <c r="M5" t="n">
-        <v>0.22</v>
+        <v>0.40375</v>
       </c>
       <c r="N5" t="n">
-        <v>31.51375</v>
+        <v>32.1175</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.3</v>
       </c>
       <c r="M6" t="n">
-        <v>0.37875</v>
+        <v>0.36375</v>
       </c>
       <c r="N6" t="n">
-        <v>25.715</v>
+        <v>25.865</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.27</v>
       </c>
       <c r="M7" t="n">
-        <v>0.335</v>
+        <v>0.34</v>
       </c>
       <c r="N7" t="n">
-        <v>19.7225</v>
+        <v>24.64375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.11</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2912500000000001</v>
+        <v>0.3525</v>
       </c>
       <c r="N8" t="n">
-        <v>17.83625</v>
+        <v>17.86375</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>0.04</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3462500000000001</v>
+        <v>0.34625</v>
       </c>
       <c r="N10" t="n">
         <v>10.82125</v>
@@ -2029,7 +2029,7 @@
         <v>0.07124999999999998</v>
       </c>
       <c r="N13" t="n">
-        <v>9.246250000000002</v>
+        <v>9.24625</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3308</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" t="n">
+        <v>62.85</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-11</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-724.68%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>47</v>
+      </c>
+      <c r="J75" t="n">
+        <v>35</v>
+      </c>
+      <c r="K75" t="n">
+        <v>30</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.25125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>19.3775</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="X75" t="n">
+        <v>49</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.2199999999999989</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.00351269359731754</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.515463917525773</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.829999999999998</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.08324715615305056</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
